--- a/INSTANCES/instances_xlsx/A_MTN_1/84FL_3A_20.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_1/84FL_3A_20.xlsx
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
